--- a/tests/testthat/fixtures/ex3/tables/irt_poly_booklet3.xlsx
+++ b/tests/testthat/fixtures/ex3/tables/irt_poly_booklet3.xlsx
@@ -145,19 +145,19 @@
     <t xml:space="preserve">step2</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.16 (0.122)</t>
+    <t xml:space="preserve">-0.16 (0.12)</t>
   </si>
   <si>
     <t xml:space="preserve">0.16</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48 (0.112)</t>
+    <t xml:space="preserve">0.48 (0.11)</t>
   </si>
   <si>
     <t xml:space="preserve">-0.48</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62 (0.12)</t>
+    <t xml:space="preserve">0.62 (0.10)</t>
   </si>
   <si>
     <t xml:space="preserve">-0.62</t>
